--- a/Team-Data/2013-14/1-21-2013-14.xlsx
+++ b/Team-Data/2013-14/1-21-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -751,7 +818,7 @@
         <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI2" t="n">
         <v>14</v>
@@ -775,7 +842,7 @@
         <v>18</v>
       </c>
       <c r="AP2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ2" t="n">
         <v>6</v>
@@ -802,7 +869,7 @@
         <v>22</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -843,37 +910,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E3" t="n">
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3" t="n">
-        <v>0.326</v>
+        <v>0.333</v>
       </c>
       <c r="H3" t="n">
         <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J3" t="n">
         <v>83</v>
       </c>
       <c r="K3" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L3" t="n">
         <v>6.2</v>
       </c>
       <c r="M3" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.328</v>
+        <v>0.332</v>
       </c>
       <c r="O3" t="n">
         <v>16.1</v>
@@ -882,16 +949,16 @@
         <v>21</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R3" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S3" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T3" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U3" t="n">
         <v>19.7</v>
@@ -900,7 +967,7 @@
         <v>15.4</v>
       </c>
       <c r="W3" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X3" t="n">
         <v>4.7</v>
@@ -909,25 +976,25 @@
         <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA3" t="n">
         <v>18.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3.7</v>
+        <v>-3.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF3" t="n">
         <v>26</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>27</v>
       </c>
       <c r="AG3" t="n">
         <v>26</v>
@@ -954,28 +1021,28 @@
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP3" t="n">
         <v>26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS3" t="n">
         <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU3" t="n">
         <v>28</v>
       </c>
       <c r="AV3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
         <v>27</v>
@@ -984,7 +1051,7 @@
         <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>22</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -1025,61 +1092,61 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
         <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>0.45</v>
+        <v>0.436</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>35.3</v>
+        <v>35.1</v>
       </c>
       <c r="J4" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M4" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="N4" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O4" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="P4" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R4" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>30.4</v>
       </c>
       <c r="T4" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="U4" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="V4" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W4" t="n">
         <v>7.3</v>
@@ -1088,25 +1155,25 @@
         <v>4.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.3</v>
+        <v>97.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.8</v>
+        <v>-3.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AE4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
         <v>18</v>
@@ -1127,7 +1194,7 @@
         <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM4" t="n">
         <v>16</v>
@@ -1142,10 +1209,10 @@
         <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS4" t="n">
         <v>23</v>
@@ -1154,31 +1221,31 @@
         <v>28</v>
       </c>
       <c r="AU4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV4" t="n">
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX4" t="n">
         <v>28</v>
       </c>
       <c r="AY4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1358,7 @@
         <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
         <v>19</v>
@@ -1315,13 +1382,13 @@
         <v>29</v>
       </c>
       <c r="AN5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO5" t="n">
         <v>9</v>
       </c>
       <c r="AP5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ5" t="n">
         <v>23</v>
@@ -1354,13 +1421,13 @@
         <v>3</v>
       </c>
       <c r="BA5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB5" t="n">
         <v>28</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>0.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
@@ -1500,7 +1567,7 @@
         <v>27</v>
       </c>
       <c r="AO6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
         <v>23</v>
@@ -1658,7 +1725,7 @@
         <v>23</v>
       </c>
       <c r="AG7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH7" t="n">
         <v>2</v>
@@ -1703,19 +1770,19 @@
         <v>29</v>
       </c>
       <c r="AV7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW7" t="n">
         <v>23</v>
       </c>
       <c r="AX7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY7" t="n">
         <v>27</v>
       </c>
       <c r="AZ7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA7" t="n">
         <v>21</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1931,7 @@
         <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP8" t="n">
         <v>27</v>
@@ -1873,10 +1940,10 @@
         <v>3</v>
       </c>
       <c r="AR8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT8" t="n">
         <v>29</v>
@@ -1885,16 +1952,16 @@
         <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ8" t="n">
         <v>12</v>
@@ -1903,7 +1970,7 @@
         <v>29</v>
       </c>
       <c r="BB8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>0.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE9" t="n">
         <v>12</v>
@@ -2031,10 +2098,10 @@
         <v>12</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL9" t="n">
         <v>10</v>
@@ -2079,10 +2146,10 @@
         <v>20</v>
       </c>
       <c r="AZ9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB9" t="n">
         <v>11</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -2195,10 +2262,10 @@
         <v>-3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF10" t="n">
         <v>19</v>
@@ -2240,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2474,7 @@
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO11" t="n">
         <v>23</v>
@@ -2443,7 +2510,7 @@
         <v>15</v>
       </c>
       <c r="AZ11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA11" t="n">
         <v>18</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2601,7 +2668,7 @@
         <v>29</v>
       </c>
       <c r="AR12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS12" t="n">
         <v>5</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>9.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2795,7 +2862,7 @@
         <v>17</v>
       </c>
       <c r="AV13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW13" t="n">
         <v>20</v>
@@ -2804,7 +2871,7 @@
         <v>4</v>
       </c>
       <c r="AY13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ13" t="n">
         <v>8</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2993,7 @@
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2947,7 +3014,7 @@
         <v>6</v>
       </c>
       <c r="AL14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM14" t="n">
         <v>7</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-5.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>21</v>
@@ -3126,7 +3193,7 @@
         <v>11</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL15" t="n">
         <v>5</v>
@@ -3153,13 +3220,13 @@
         <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU15" t="n">
         <v>10</v>
       </c>
       <c r="AV15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW15" t="n">
         <v>28</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
         <v>12</v>
@@ -3299,7 +3366,7 @@
         <v>12</v>
       </c>
       <c r="AH16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI16" t="n">
         <v>17</v>
@@ -3317,13 +3384,13 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP16" t="n">
         <v>25</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>24</v>
       </c>
       <c r="AQ16" t="n">
         <v>20</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F17" t="n">
         <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>0.714</v>
+        <v>0.707</v>
       </c>
       <c r="H17" t="n">
         <v>48.6</v>
@@ -3409,37 +3476,37 @@
         <v>38.9</v>
       </c>
       <c r="J17" t="n">
-        <v>76.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="K17" t="n">
         <v>0.506</v>
       </c>
       <c r="L17" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.373</v>
+        <v>0.376</v>
       </c>
       <c r="O17" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="P17" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
       <c r="R17" t="n">
         <v>7.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T17" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="U17" t="n">
         <v>23.5</v>
@@ -3463,13 +3530,13 @@
         <v>21.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>104</v>
+        <v>104.2</v>
       </c>
       <c r="AC17" t="n">
         <v>5.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3493,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AM17" t="n">
         <v>14</v>
@@ -3502,7 +3569,7 @@
         <v>7</v>
       </c>
       <c r="AO17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
@@ -3514,13 +3581,13 @@
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV17" t="n">
         <v>16</v>
@@ -3538,10 +3605,10 @@
         <v>9</v>
       </c>
       <c r="BA17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC17" t="n">
         <v>6</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3669,7 +3736,7 @@
         <v>29</v>
       </c>
       <c r="AJ18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK18" t="n">
         <v>30</v>
@@ -3681,7 +3748,7 @@
         <v>17</v>
       </c>
       <c r="AN18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO18" t="n">
         <v>29</v>
@@ -3693,7 +3760,7 @@
         <v>17</v>
       </c>
       <c r="AR18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AS18" t="n">
         <v>28</v>
@@ -3702,13 +3769,13 @@
         <v>25</v>
       </c>
       <c r="AU18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX18" t="n">
         <v>7</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -3755,19 +3822,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F19" t="n">
         <v>21</v>
       </c>
       <c r="G19" t="n">
-        <v>0.488</v>
+        <v>0.475</v>
       </c>
       <c r="H19" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I19" t="n">
         <v>38.7</v>
@@ -3782,40 +3849,40 @@
         <v>7.8</v>
       </c>
       <c r="M19" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0.347</v>
+        <v>0.346</v>
       </c>
       <c r="O19" t="n">
         <v>21.2</v>
       </c>
       <c r="P19" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.785</v>
+        <v>0.782</v>
       </c>
       <c r="R19" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="S19" t="n">
         <v>32.6</v>
       </c>
       <c r="T19" t="n">
-        <v>46</v>
+        <v>46.2</v>
       </c>
       <c r="U19" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="V19" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Y19" t="n">
         <v>5.8</v>
@@ -3827,16 +3894,16 @@
         <v>22.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.5</v>
+        <v>106.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE19" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AF19" t="n">
         <v>17</v>
@@ -3845,7 +3912,7 @@
         <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
         <v>7</v>
@@ -3857,7 +3924,7 @@
         <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM19" t="n">
         <v>12</v>
@@ -3884,7 +3951,7 @@
         <v>3</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
         <v>7</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -3937,61 +4004,61 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E20" t="n">
         <v>16</v>
       </c>
       <c r="F20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G20" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="H20" t="n">
         <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J20" t="n">
-        <v>84.7</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K20" t="n">
         <v>0.454</v>
       </c>
       <c r="L20" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M20" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="N20" t="n">
-        <v>0.386</v>
+        <v>0.385</v>
       </c>
       <c r="O20" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="P20" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.764</v>
+        <v>0.768</v>
       </c>
       <c r="R20" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S20" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T20" t="n">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
       <c r="U20" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V20" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W20" t="n">
         <v>8.300000000000001</v>
@@ -4003,25 +4070,25 @@
         <v>6.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.7</v>
+        <v>100.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-2.2</v>
+        <v>-1.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
         <v>21</v>
       </c>
       <c r="AF20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG20" t="n">
         <v>21</v>
@@ -4030,10 +4097,10 @@
         <v>11</v>
       </c>
       <c r="AI20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AK20" t="n">
         <v>11</v>
@@ -4045,52 +4112,52 @@
         <v>28</v>
       </c>
       <c r="AN20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO20" t="n">
         <v>15</v>
       </c>
       <c r="AP20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR20" t="n">
         <v>4</v>
       </c>
       <c r="AS20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW20" t="n">
         <v>10</v>
       </c>
       <c r="AX20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
       </c>
       <c r="AZ20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB20" t="n">
         <v>15</v>
       </c>
       <c r="BC20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE21" t="n">
         <v>23</v>
@@ -4206,10 +4273,10 @@
         <v>23</v>
       </c>
       <c r="AG21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI21" t="n">
         <v>26</v>
@@ -4236,7 +4303,7 @@
         <v>28</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR21" t="n">
         <v>20</v>
@@ -4248,7 +4315,7 @@
         <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV21" t="n">
         <v>2</v>
@@ -4263,7 +4330,7 @@
         <v>6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA21" t="n">
         <v>22</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -4301,76 +4368,76 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E22" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F22" t="n">
         <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>0.762</v>
+        <v>0.756</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
       </c>
       <c r="I22" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J22" t="n">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0.466</v>
       </c>
       <c r="L22" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M22" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.349</v>
+        <v>0.343</v>
       </c>
       <c r="O22" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="P22" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="R22" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S22" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="T22" t="n">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
       <c r="U22" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V22" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="W22" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Y22" t="n">
         <v>4</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AB22" t="n">
         <v>105.3</v>
@@ -4379,10 +4446,10 @@
         <v>7.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF22" t="n">
         <v>3</v>
@@ -4409,7 +4476,7 @@
         <v>20</v>
       </c>
       <c r="AN22" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AO22" t="n">
         <v>4</v>
@@ -4421,7 +4488,7 @@
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS22" t="n">
         <v>1</v>
@@ -4433,19 +4500,19 @@
         <v>16</v>
       </c>
       <c r="AV22" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW22" t="n">
         <v>11</v>
       </c>
       <c r="AX22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY22" t="n">
         <v>7</v>
       </c>
       <c r="AZ22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -4483,43 +4550,43 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E23" t="n">
         <v>11</v>
       </c>
       <c r="F23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G23" t="n">
-        <v>0.262</v>
+        <v>0.268</v>
       </c>
       <c r="H23" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="I23" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J23" t="n">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L23" t="n">
         <v>7.2</v>
       </c>
       <c r="M23" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O23" t="n">
         <v>16.1</v>
       </c>
       <c r="P23" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q23" t="n">
         <v>0.753</v>
@@ -4531,16 +4598,16 @@
         <v>33.3</v>
       </c>
       <c r="T23" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="U23" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V23" t="n">
         <v>15.2</v>
       </c>
       <c r="W23" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X23" t="n">
         <v>4.3</v>
@@ -4549,19 +4616,19 @@
         <v>5.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.90000000000001</v>
+        <v>96</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6</v>
+        <v>-5.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4573,13 +4640,13 @@
         <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI23" t="n">
         <v>23</v>
       </c>
       <c r="AJ23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="n">
         <v>21</v>
@@ -4594,10 +4661,10 @@
         <v>25</v>
       </c>
       <c r="AO23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ23" t="n">
         <v>19</v>
@@ -4609,7 +4676,7 @@
         <v>8</v>
       </c>
       <c r="AT23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU23" t="n">
         <v>20</v>
@@ -4621,7 +4688,7 @@
         <v>16</v>
       </c>
       <c r="AX23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AY23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,13 +4822,13 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI24" t="n">
         <v>4</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK24" t="n">
         <v>19</v>
@@ -4779,7 +4846,7 @@
         <v>20</v>
       </c>
       <c r="AP24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4940,7 +5007,7 @@
         <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ25" t="n">
         <v>6</v>
@@ -4979,7 +5046,7 @@
         <v>30</v>
       </c>
       <c r="AV25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW25" t="n">
         <v>7</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E26" t="n">
         <v>31</v>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G26" t="n">
-        <v>0.738</v>
+        <v>0.756</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5047,28 +5114,28 @@
         <v>40.5</v>
       </c>
       <c r="J26" t="n">
-        <v>88.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L26" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="M26" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="N26" t="n">
         <v>0.395</v>
       </c>
       <c r="O26" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="P26" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.822</v>
+        <v>0.825</v>
       </c>
       <c r="R26" t="n">
         <v>13</v>
@@ -5077,55 +5144,55 @@
         <v>33.6</v>
       </c>
       <c r="T26" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="U26" t="n">
         <v>24.5</v>
       </c>
       <c r="V26" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W26" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="X26" t="n">
         <v>4.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AA26" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>109.3</v>
+        <v>109.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK26" t="n">
         <v>9</v>
@@ -5170,13 +5237,13 @@
         <v>18</v>
       </c>
       <c r="AY26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
         <v>4</v>
       </c>
       <c r="BA26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB26" t="n">
         <v>1</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F27" t="n">
         <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>0.375</v>
+        <v>0.359</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J27" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.451</v>
+        <v>0.449</v>
       </c>
       <c r="L27" t="n">
         <v>6.8</v>
@@ -5241,28 +5308,28 @@
         <v>19.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.35</v>
+        <v>0.348</v>
       </c>
       <c r="O27" t="n">
         <v>19.7</v>
       </c>
       <c r="P27" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.771</v>
+        <v>0.774</v>
       </c>
       <c r="R27" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S27" t="n">
         <v>31.8</v>
       </c>
       <c r="T27" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U27" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V27" t="n">
         <v>15</v>
@@ -5271,34 +5338,34 @@
         <v>7.7</v>
       </c>
       <c r="X27" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Y27" t="n">
         <v>5.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.8</v>
+        <v>101.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>-1.9</v>
+        <v>-2.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AE27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AH27" t="n">
         <v>14</v>
@@ -5307,10 +5374,10 @@
         <v>15</v>
       </c>
       <c r="AJ27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL27" t="n">
         <v>23</v>
@@ -5319,13 +5386,13 @@
         <v>24</v>
       </c>
       <c r="AN27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="n">
         <v>5</v>
       </c>
       <c r="AP27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ27" t="n">
         <v>7</v>
@@ -5340,10 +5407,10 @@
         <v>13</v>
       </c>
       <c r="AU27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW27" t="n">
         <v>14</v>
@@ -5355,7 +5422,7 @@
         <v>25</v>
       </c>
       <c r="AZ27" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BA27" t="n">
         <v>4</v>
@@ -5364,7 +5431,7 @@
         <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5665,19 +5732,19 @@
         <v>12</v>
       </c>
       <c r="AH29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK29" t="n">
         <v>24</v>
       </c>
       <c r="AL29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM29" t="n">
         <v>11</v>
@@ -5710,7 +5777,7 @@
         <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX29" t="n">
         <v>19</v>
@@ -5719,7 +5786,7 @@
         <v>17</v>
       </c>
       <c r="AZ29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA29" t="n">
         <v>5</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E30" t="n">
         <v>14</v>
       </c>
       <c r="F30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>0.326</v>
+        <v>0.333</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
       </c>
       <c r="I30" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J30" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L30" t="n">
         <v>6.6</v>
@@ -5787,19 +5854,19 @@
         <v>18.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O30" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="P30" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R30" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S30" t="n">
         <v>30.3</v>
@@ -5814,34 +5881,34 @@
         <v>15.1</v>
       </c>
       <c r="W30" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X30" t="n">
         <v>4.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA30" t="n">
         <v>20.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>-6.7</v>
+        <v>-6.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF30" t="n">
         <v>26</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>27</v>
       </c>
       <c r="AG30" t="n">
         <v>26</v>
@@ -5850,13 +5917,13 @@
         <v>24</v>
       </c>
       <c r="AI30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ30" t="n">
         <v>24</v>
       </c>
       <c r="AK30" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5868,19 +5935,19 @@
         <v>16</v>
       </c>
       <c r="AO30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ30" t="n">
         <v>18</v>
       </c>
       <c r="AR30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS30" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AT30" t="n">
         <v>24</v>
@@ -5892,7 +5959,7 @@
         <v>17</v>
       </c>
       <c r="AW30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AX30" t="n">
         <v>13</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6035,13 +6102,13 @@
         <v>16</v>
       </c>
       <c r="AJ31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK31" t="n">
         <v>16</v>
       </c>
       <c r="AL31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM31" t="n">
         <v>18</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-21-2013-14</t>
+          <t>2014-01-21</t>
         </is>
       </c>
     </row>
